--- a/TMUiZone/Uploads/OD_UploadFormat.xlsx
+++ b/TMUiZone/Uploads/OD_UploadFormat.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\TALLYSERVER\User profile Data$\Acc019\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6630"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Update" sheetId="4" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Update!$A$1:$AA$5</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>RowNumber</t>
   </si>
@@ -53,26 +56,56 @@
     <t>Remark</t>
   </si>
   <si>
-    <t>tmu05573</t>
-  </si>
-  <si>
-    <t>BHUPENDRA SINGH</t>
-  </si>
-  <si>
     <t>OD</t>
   </si>
   <si>
-    <t>xyz</t>
+    <t>TMU00157</t>
+  </si>
+  <si>
+    <t>SHALINI BANSAL</t>
+  </si>
+  <si>
+    <t>TMU03444</t>
+  </si>
+  <si>
+    <t>SHIKHA PALIWAL</t>
+  </si>
+  <si>
+    <t>TMU03447</t>
+  </si>
+  <si>
+    <t>PINAKI ADAK</t>
+  </si>
+  <si>
+    <t>TMU03953</t>
+  </si>
+  <si>
+    <t>RUBY KHATOON</t>
+  </si>
+  <si>
+    <t>Punch Correction</t>
+  </si>
+  <si>
+    <t>Dir HR</t>
+  </si>
+  <si>
+    <t>Dir Account</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -95,20 +128,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -386,21 +418,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,331 +462,192 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46246</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46246</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2">
+        <f t="shared" ref="J2:J5" si="0">E2-D2+1</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46256</v>
+      </c>
+      <c r="E3" s="3">
+        <v>46256</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46256</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46256</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2">
-        <v>45960</v>
-      </c>
-      <c r="E2" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D5" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E5" s="3">
+        <v>46235</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
-        <v>45961</v>
-      </c>
-      <c r="E3" s="2">
-        <v>45961</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2">
-        <v>45960</v>
-      </c>
-      <c r="E4" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2">
-        <v>45961</v>
-      </c>
-      <c r="E5" s="2">
-        <v>45961</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2">
-        <v>45960</v>
-      </c>
-      <c r="E6" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2">
-        <v>45961</v>
-      </c>
-      <c r="E7" s="2">
-        <v>45961</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2">
-        <v>45960</v>
-      </c>
-      <c r="E8" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2">
-        <v>45961</v>
-      </c>
-      <c r="E9" s="2">
-        <v>45961</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2">
-        <v>45960</v>
-      </c>
-      <c r="E10" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2">
-        <v>45961</v>
-      </c>
-      <c r="E11" s="2">
-        <v>45961</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2">
-        <v>45960</v>
-      </c>
-      <c r="E12" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2">
-        <v>45961</v>
-      </c>
-      <c r="E13" s="2">
-        <v>45961</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="1"/>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>